--- a/out/Attention-mamba2_repeat_3_000008.xlsx
+++ b/out/Attention-mamba2_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001122823411441641</v>
+        <v>-8.092237725213636e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1289908441631052</v>
+        <v>-0.09296426888755301</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.138476860958186</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5384768609581863</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5384768609581863</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1292020456355866</v>
+        <v>-0.09313047883650044</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3556904116388132</v>
+        <v>0.3066744276266828</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5828622307362086</v>
+        <v>0.5208077170268269</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0253428671499572</v>
+        <v>0.02185048858028902</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2772865459540314</v>
+        <v>0.2573418861358664</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04444275413111387</v>
+        <v>0.03831831204703041</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3408209133055024</v>
+        <v>0.3121209133766643</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05399269762169234</v>
+        <v>0.04655222378040122</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4043596931510621</v>
+        <v>0.3669037703676382</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01428782058839201</v>
+        <v>0.0123188847874462</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.378873408339232</v>
+        <v>0.3449295873102571</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007936690539256379</v>
+        <v>0.006842309660677279</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.380446142058555</v>
+        <v>0.346284906159864</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01667723964968019</v>
+        <v>0.01437946767453237</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4058745940539718</v>
+        <v>0.3682089861996181</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006549330454790059</v>
+        <v>0.005645869531051445</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4022808997837226</v>
+        <v>0.3651099641255264</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004662674475779064</v>
+        <v>0.004019273670359408</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4050541873009158</v>
+        <v>0.3675002873988496</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00183222679203809</v>
+        <v>0.001578301137853963</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4040523336550754</v>
+        <v>0.3666358427882474</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001036995300898401</v>
+        <v>0.0008936438763665205</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4042945693233185</v>
+        <v>0.3668440905436238</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000391936799970422</v>
+        <v>0.0003379158153590628</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4040402471460903</v>
+        <v>0.3666240172591431</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001810623149373331</v>
+        <v>0.0001557402247387611</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4040100791300293</v>
+        <v>0.3665973379704726</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.362265002008783e-05</v>
+        <v>5.393474648784013e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4039550041514612</v>
+        <v>0.3665493324006437</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.503340156967809e-05</v>
+        <v>1.217148705972408e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4039218602802509</v>
+        <v>0.3665201618344027</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4039168446427682</v>
+        <v>0.3665151484308459</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4039126444334458</v>
+        <v>0.3665108395535285</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4039096605543401</v>
+        <v>0.3665076719319637</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4039042168093337</v>
+        <v>0.3665023026049759</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4038982240759034</v>
+        <v>0.3664963098715455</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.403892856287325</v>
+        <v>0.3664909420829671</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4038928930358167</v>
+        <v>0.3664909788314588</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4038930032812923</v>
+        <v>0.3664910890769344</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4038930767782759</v>
+        <v>0.366491162573918</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.403893260520735</v>
+        <v>0.3664913463163771</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4038948039573915</v>
+        <v>0.3664928897530336</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5384768609581863</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4038962738970646</v>
+        <v>0.3664943596927067</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5384768609581863</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4038975233457866</v>
+        <v>0.3664956091414287</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4038988830399839</v>
+        <v>0.366496968835626</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4038966781304746</v>
+        <v>0.3664947639261167</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4038962738970646</v>
+        <v>0.3664943596927067</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4038954286817527</v>
+        <v>0.3664935144773948</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.138476860958186</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4038959799091299</v>
+        <v>0.366494065704772</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.138476860958186</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4038956491727035</v>
+        <v>0.3664937349683456</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.403895355184769</v>
+        <v>0.3664934409804111</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4038954286817527</v>
+        <v>0.3664935144773948</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4038949876998507</v>
+        <v>0.3664930734954928</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4038948774543751</v>
+        <v>0.3664929632500172</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4038948407058834</v>
+        <v>0.3664929265015255</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.637571854792519</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4038949876998507</v>
+        <v>0.3664930734954928</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.403894509969457</v>
+        <v>0.3664925957650992</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4038954654302443</v>
+        <v>0.3664935512258864</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4038954286817527</v>
+        <v>0.3664935144773948</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4038950979453262</v>
+        <v>0.3664931837409683</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4038955389272282</v>
+        <v>0.3664936247228703</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4038949142028671</v>
+        <v>0.3664929999985092</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4038947304604079</v>
+        <v>0.36649281625605</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4038943262269979</v>
+        <v>0.36649241202264</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4038934810116859</v>
+        <v>0.366491566807328</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4038934442631942</v>
+        <v>0.3664915300588363</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4038935912571615</v>
+        <v>0.3664916770528036</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4038935177601778</v>
+        <v>0.3664916035558199</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4038935912571615</v>
+        <v>0.3664916770528036</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4038936280056534</v>
+        <v>0.3664917138012955</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4038935177601778</v>
+        <v>0.3664916035558199</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4038939587420798</v>
+        <v>0.3664920445377219</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4038938484966043</v>
+        <v>0.3664919342922464</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4038938117481123</v>
+        <v>0.3664918975437544</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4038937382511287</v>
+        <v>0.3664918240467708</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.403893701502637</v>
+        <v>0.3664917872982791</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4038934810116859</v>
+        <v>0.366491566807328</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4038934075147023</v>
+        <v>0.3664914933103444</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4038933340177187</v>
+        <v>0.3664914198133608</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4038933707662106</v>
+        <v>0.3664914565618527</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.403893260520735</v>
+        <v>0.3664913463163771</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4038933707662106</v>
+        <v>0.3664914565618527</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4038936647541451</v>
+        <v>0.3664917505497872</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000008.xlsx
+++ b/out/Attention-mamba2_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.637571854792519</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.637571854792519</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001122823411441641</v>
+        <v>-9.334513270214666e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1289908441631052</v>
+        <v>-0.1072356288894445</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.138476860958186</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1073289740221465</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1292020456355866</v>
+        <v>-0.1074289545489647</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3556904116388132</v>
+        <v>0.3595072048122351</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5828622307362086</v>
+        <v>0.6122757220734482</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0253428671499572</v>
+        <v>0.02561477627593958</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2772865459540314</v>
+        <v>0.3034214541312861</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04444275413111387</v>
+        <v>0.04491959009290683</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3408209133055024</v>
+        <v>0.3676374935379713</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05399269762169234</v>
+        <v>0.05457199700139059</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4043596931510621</v>
+        <v>0.4318579908099398</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01428782058839201</v>
+        <v>0.01444128273177783</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.378873408339232</v>
+        <v>0.4060982609119881</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007936690539256379</v>
+        <v>0.008021804975672855</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.380446142058555</v>
+        <v>0.4076879038669041</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01667723964968019</v>
+        <v>0.0168559848958562</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.4757798495655082</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4058745940539718</v>
+        <v>0.4333888832596292</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006549330454790059</v>
+        <v>0.0066195727250003</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4022808997837226</v>
+        <v>0.4297567292207777</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004662674475779064</v>
+        <v>0.00471269759469909</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4050541873009158</v>
+        <v>0.4325597914378967</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00183222679203809</v>
+        <v>0.001851237268821928</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4040523336550754</v>
+        <v>0.4315472554874469</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001036995300898401</v>
+        <v>0.001049326606234477</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4042945693233185</v>
+        <v>0.4317922311046603</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000391936799970422</v>
+        <v>0.0003966342768931489</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4040402471460903</v>
+        <v>0.4315353302029739</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001810623149373331</v>
+        <v>0.0001832642358241654</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4040100791300293</v>
+        <v>0.4315049387073396</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4039550041514612</v>
+        <v>0.431449569740837</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.503340156967809e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4039218602802509</v>
+        <v>0.431416094388558</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.09174968847840292</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4039168446427682</v>
+        <v>0.4314110787510753</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4039126444334458</v>
+        <v>0.4314068785417529</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4039096605543401</v>
+        <v>0.4314038946626473</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.09174968847840292</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4039042168093337</v>
+        <v>0.431398450917641</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.09174968847840298</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4038982240759034</v>
+        <v>0.4313924581842106</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.403892856287325</v>
+        <v>0.4313870903956322</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4038928930358167</v>
+        <v>0.4313871271441239</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4038930032812923</v>
+        <v>0.4313872373895994</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4038930767782759</v>
+        <v>0.4313873108865831</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.09174968847840287</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.403893260520735</v>
+        <v>0.4313874946290422</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.09174968847840287</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4038948039573915</v>
+        <v>0.4313890380656987</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4038962738970646</v>
+        <v>0.4313905080053718</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4038975233457866</v>
+        <v>0.4313917574540938</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4038988830399839</v>
+        <v>0.4313931171482911</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4038966781304746</v>
+        <v>0.4313909122387818</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4038962738970646</v>
+        <v>0.4313905080053718</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4038954286817527</v>
+        <v>0.4313896627900598</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4038959799091299</v>
+        <v>0.431390214017437</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.09174968847840287</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4038956491727035</v>
+        <v>0.4313898832810107</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.403895355184769</v>
+        <v>0.4313895892930762</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4038954286817527</v>
+        <v>0.4313896627900598</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4038949876998507</v>
+        <v>0.4313892218081579</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4038948774543751</v>
+        <v>0.4313891115626823</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4038948407058834</v>
+        <v>0.4313890748141906</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4038949876998507</v>
+        <v>0.4313892218081579</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.403894509969457</v>
+        <v>0.4313887440777642</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4038954654302443</v>
+        <v>0.4313896995385515</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4038954286817527</v>
+        <v>0.4313896627900598</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.859279226522314</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4038950979453262</v>
+        <v>0.4313893320536334</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4038955389272282</v>
+        <v>0.4313897730355353</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4038949142028671</v>
+        <v>0.4313891483111743</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4038947304604079</v>
+        <v>0.4313889645687151</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4038943262269979</v>
+        <v>0.431388560335305</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4038934810116859</v>
+        <v>0.4313877151199931</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.826808764566225</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4038934442631942</v>
+        <v>0.4313876783715014</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.059279226522314</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4038935912571615</v>
+        <v>0.4313878253654686</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.859279226522314</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4038935177601778</v>
+        <v>0.431387751868485</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.09174968847840287</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4038935912571615</v>
+        <v>0.4313878253654686</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.859279226522314</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4038936280056534</v>
+        <v>0.4313878621139606</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.09174968847840287</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4038935177601778</v>
+        <v>0.431387751868485</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.09174968847840287</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4038939587420798</v>
+        <v>0.4313881928503869</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-2.037571854792519</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4038938484966043</v>
+        <v>0.4313880826049114</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4038938117481123</v>
+        <v>0.4313880458564195</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4038937382511287</v>
+        <v>0.4313879723594359</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.403893701502637</v>
+        <v>0.4313879356109442</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4038934810116859</v>
+        <v>0.4313877151199931</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4038934075147023</v>
+        <v>0.4313876416230095</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4038933340177187</v>
+        <v>0.4313875681260259</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.138476860958186</v>
+        <v>0.6757798495655083</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4038933707662106</v>
+        <v>0.4313876048745178</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.403893260520735</v>
+        <v>0.4313874946290422</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.2917496884784029</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4038933707662106</v>
+        <v>0.4313876048745178</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.6755144575003584</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4038936647541451</v>
+        <v>0.4313878988624523</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000008.xlsx
+++ b/out/Attention-mamba2_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1721755564212799</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.826808764566225</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1951287537813187</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04375836998224258</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.02476336434483528</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.08127033710479736</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.1818867027759552</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.1852529644966125</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.1862178891897202</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.1849252581596375</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.1849012821912766</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.1833620965480804</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.1831473559141159</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.1823184341192245</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.1801310479640961</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.176223948597908</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.1881598681211472</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.1808888167142868</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.1800243556499481</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.1798338741064072</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.1774735301733017</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.177413672208786</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.1774521172046661</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.1777246743440628</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.1805776208639145</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.1806277930736542</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.1776551753282547</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.1778765022754669</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.1772389560937881</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.1787219643592834</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.1781488507986069</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.1521632373332977</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.1873824000358582</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.1859348118305206</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.1839710623025894</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.1831587702035904</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4757798495655082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.1833113431930542</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.1796306818723679</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.1780135780572891</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.1844035536050797</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.1801699995994568</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.1774719804525375</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.08915553987026215</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0254511646926403</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.05524997040629387</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.334513270214666e-05</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1072356288894445</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.03943484276533127</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02347634546458721</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.06575620174407959</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.1079628020524979</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.1153795570135117</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.1179036647081375</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.1113886386156082</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.1094008535146713</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.08899477124214172</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.08068200945854187</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.05303644016385078</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.02999742701649666</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.04303308948874474</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1073289740221465</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03923188894987106</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1074289545489647</v>
+        <v>-0.08882259802308166</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3595072048122351</v>
+        <v>0.2450100850180599</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04151949286460876</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6122757220734482</v>
+        <v>0.4016685148271203</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02561477627593958</v>
+        <v>0.01745691711621853</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.03061726316809654</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3034214541312861</v>
+        <v>0.191178799990556</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04491959009290683</v>
+        <v>0.03061348468161163</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01661251857876778</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3676374935379713</v>
+        <v>0.2349432102014082</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05457199700139059</v>
+        <v>0.03719176846430827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.003053061664104462</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4318579908099398</v>
+        <v>0.2787107170440257</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01444128273177783</v>
+        <v>0.009841275378308329</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.004802487790584564</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4060982609119881</v>
+        <v>0.2611541543437242</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008021804975672855</v>
+        <v>0.005465436902612457</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02696821093559265</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4076879038669041</v>
+        <v>0.2622359371537592</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0168559848958562</v>
+        <v>0.01148623516005559</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01559442281723022</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4757798495655082</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4333888832596292</v>
+        <v>0.2797504684094372</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0066195727250003</v>
+        <v>0.004509882471444446</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>-0.002549130469560623</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4297567292207777</v>
+        <v>0.2772734336275656</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00471269759469909</v>
+        <v>0.00321027909196311</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0004649832844734192</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4325597914378967</v>
+        <v>0.2791822281331267</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001851237268821928</v>
+        <v>0.001260554597324094</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01427598670125008</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4315472554874469</v>
+        <v>0.2784905558508476</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001049326606234477</v>
+        <v>0.0007132985358264126</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.005550052970647812</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4317922311046603</v>
+        <v>0.27865586087661</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003966342768931489</v>
+        <v>0.0002686280307488412</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003366231918334961</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4315353302029739</v>
+        <v>0.2784792441804321</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001832642358241654</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.006208177655935287</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4315049387073396</v>
+        <v>0.2784569460431346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.362265002008783e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.006376218050718307</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.431449569740837</v>
+        <v>0.278417483246295</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00506109744310379</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.431416094388558</v>
+        <v>0.2783929482025178</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.005635648965835571</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.09174968847840292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4314110787510753</v>
+        <v>0.278387937032887</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.009151063859462738</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4314068785417529</v>
+        <v>0.2783834827390828</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01376615092158318</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.6757798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4314038946626473</v>
+        <v>0.2783799486418308</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01669330894947052</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.09174968847840292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.431398450917641</v>
+        <v>0.2783746528118267</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.002577651292085648</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.09174968847840298</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4313924581842106</v>
+        <v>0.278368990814823</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.02316978201270103</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4313870903956322</v>
+        <v>0.2783688070723638</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.007328670471906662</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4313871271441239</v>
+        <v>0.2783688438208555</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02442637830972672</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2917496884784029</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4313872373895994</v>
+        <v>0.2783689540663311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01576020196080208</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4313873108865831</v>
+        <v>0.2783690275633147</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01732603460550308</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.09174968847840287</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4313874946290422</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02423679456114769</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.09174968847840287</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4313890380656987</v>
+        <v>0.2783707547424303</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02129619941115379</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2917496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4313905080053718</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.02239086478948593</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4313917574540938</v>
+        <v>0.2783734741308254</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.004268940538167953</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4313931171482911</v>
+        <v>0.2783748338250227</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0498722605407238</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4313909122387818</v>
+        <v>0.2783726289155134</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01099774613976479</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4313905080053718</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.03551267087459564</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4313896627900598</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.02101528644561768</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.431390214017437</v>
+        <v>0.2783719306941687</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.002261895686388016</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.09174968847840287</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4313898832810107</v>
+        <v>0.2783715999577422</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0054205022752285</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4313895892930762</v>
+        <v>0.2783713059698078</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01214448735117912</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4313896627900598</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.005838979035615921</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4313892218081579</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.003923472017049789</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4313891115626823</v>
+        <v>0.2783708282394139</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.0004674419760704041</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4313890748141906</v>
+        <v>0.2783707914909222</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.004841025918722153</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4313892218081579</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0158076323568821</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.059279226522314</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4313887440777642</v>
+        <v>0.2783704607544958</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001312863081693649</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2917496884784029</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4313896995385515</v>
+        <v>0.2783714162152831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.005732234567403793</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.059279226522314</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4313896627900598</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00528142973780632</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.859279226522314</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4313893320536334</v>
+        <v>0.278371048730365</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004568841308355331</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4313897730355353</v>
+        <v>0.2783714897122669</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.008046429604291916</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4313891483111743</v>
+        <v>0.2783708649879058</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01021180674433708</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4313889645687151</v>
+        <v>0.2783706812454467</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01806877925992012</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.431388560335305</v>
+        <v>0.2783702770120366</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01431823894381523</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4313877151199931</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002426590770483017</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.826808764566225</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4313876783715014</v>
+        <v>0.278369395048233</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01382211223244667</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.059279226522314</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4313878253654686</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.00118589773774147</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.859279226522314</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.431387751868485</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002997376024723053</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.09174968847840287</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4313878253654686</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.006336085498332977</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.859279226522314</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4313878621139606</v>
+        <v>0.2783695787906921</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02107853814959526</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.09174968847840287</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.431387751868485</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.009466860443353653</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.09174968847840287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4313881928503869</v>
+        <v>0.2783699095271185</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.008116502314805984</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4313880826049114</v>
+        <v>0.278369799281643</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01227801293134689</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4313880458564195</v>
+        <v>0.2783697625331511</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01355800777673721</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4313879723594359</v>
+        <v>0.2783696890361674</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01575061678886414</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4313879356109442</v>
+        <v>0.2783696522876757</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.01169585064053535</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4313877151199931</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01604077965021133</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4313876416230095</v>
+        <v>0.2783693582997411</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0147521011531353</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4313875681260259</v>
+        <v>0.2783692848027574</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01689591258764267</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6757798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4313876048745178</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.005618546158075333</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4313874946290422</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01448942348361015</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2917496884784029</v>
+        <v>-0.1600000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4313876048745178</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.03651267662644386</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6755144575003584</v>
+        <v>-0.3000000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4313878988624523</v>
+        <v>0.2783696155391838</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000008.xlsx
+++ b/out/Attention-mamba2_repeat_3_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1721755564212799</v>
+        <v>-0.1723965257406235</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1951287537813187</v>
+        <v>-0.1956609785556793</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.04375836998224258</v>
+        <v>0.04220360144972801</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.02476336434483528</v>
+        <v>0.02458283305168152</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.08127033710479736</v>
+        <v>0.08175403624773026</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.16</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.1818867027759552</v>
+        <v>0.1825547516345978</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.1852529644966125</v>
+        <v>0.1858389973640442</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.1862178891897202</v>
+        <v>0.1867620050907135</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.1849252581596375</v>
+        <v>0.1854700148105621</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.1849012821912766</v>
+        <v>0.1854281276464462</v>
       </c>
       <c r="JB11" t="n">
         <v>0.8599999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.1833620965480804</v>
+        <v>0.1838867366313934</v>
       </c>
       <c r="JB12" t="n">
         <v>0.7199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.1831473559141159</v>
+        <v>0.1836739480495453</v>
       </c>
       <c r="JB13" t="n">
         <v>0.5799999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.1823184341192245</v>
+        <v>0.1828330308198929</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.16</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.1801310479640961</v>
+        <v>0.1806559711694717</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.176223948597908</v>
+        <v>0.176843598484993</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.1881598681211472</v>
+        <v>0.1887263208627701</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.1808888167142868</v>
+        <v>0.1813800930976868</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.1800243556499481</v>
+        <v>0.1805176585912704</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.02000000000000007</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.1798338741064072</v>
+        <v>0.1803257763385773</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.16</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.1774735301733017</v>
+        <v>0.1779546588659286</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.16</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.177413672208786</v>
+        <v>0.1778978109359741</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.16</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.1774521172046661</v>
+        <v>0.1779363751411438</v>
       </c>
       <c r="JB23" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.1777246743440628</v>
+        <v>0.1782114058732986</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.1805776208639145</v>
+        <v>0.1810785830020905</v>
       </c>
       <c r="JB25" t="n">
         <v>0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.1806277930736542</v>
+        <v>0.18112713098526</v>
       </c>
       <c r="JB26" t="n">
         <v>0.8599999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.1776551753282547</v>
+        <v>0.17813940346241</v>
       </c>
       <c r="JB27" t="n">
         <v>0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.1778765022754669</v>
+        <v>0.1783621907234192</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.1772389560937881</v>
+        <v>0.1777617633342743</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.1787219643592834</v>
+        <v>0.1792138963937759</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.1781488507986069</v>
+        <v>0.1786856800317764</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.1521632373332977</v>
+        <v>0.1528077274560928</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.02000000000000007</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.1873824000358582</v>
+        <v>0.1879879683256149</v>
       </c>
       <c r="JB33" t="n">
         <v>0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.1859348118305206</v>
+        <v>0.1864680200815201</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.1839710623025894</v>
+        <v>0.1844904720783234</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.1831587702035904</v>
+        <v>0.1836735755205154</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.1833113431930542</v>
+        <v>0.1838298588991165</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.16</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.1796306818723679</v>
+        <v>0.1801233142614365</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.1780135780572891</v>
+        <v>0.1785175651311874</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.1844035536050797</v>
+        <v>0.1849639266729355</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.1801699995994568</v>
+        <v>0.1807657927274704</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.1774719804525375</v>
+        <v>0.1780984401702881</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.08915553987026215</v>
+        <v>0.08988982439041138</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0254511646926403</v>
+        <v>-0.02528189495205879</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.05524997040629387</v>
+        <v>0.05379796028137207</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.03943484276533127</v>
+        <v>0.03796713799238205</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.02347634546458721</v>
+        <v>0.02343807369470596</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.06575620174407959</v>
+        <v>0.06702711433172226</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.1079628020524979</v>
+        <v>0.1090470999479294</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.1153795570135117</v>
+        <v>0.1162869036197662</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.1179036647081375</v>
+        <v>0.1187228113412857</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1113886386156082</v>
+        <v>0.1123017221689224</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.1094008535146713</v>
+        <v>0.1104293763637543</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.08899477124214172</v>
+        <v>0.09005005657672882</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.08068200945854187</v>
+        <v>0.08182166516780853</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.05303644016385078</v>
+        <v>0.05416031181812286</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.02999742701649666</v>
+        <v>0.03100789710879326</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.04303308948874474</v>
+        <v>0.04265113174915314</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.03923188894987106</v>
+        <v>0.03781330958008766</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.04151949286460876</v>
+        <v>0.04032241925597191</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.03061726316809654</v>
+        <v>0.02941020578145981</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01661251857876778</v>
+        <v>0.01543931663036346</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.003053061664104462</v>
+        <v>0.01428210735321045</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.004802487790584564</v>
+        <v>0.00404016301035881</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.02696821093559265</v>
+        <v>0.02583438158035278</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.01559442281723022</v>
+        <v>0.0145605280995369</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002549130469560623</v>
+        <v>0.01385434716939926</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0004649832844734192</v>
+        <v>-0.00121365487575531</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.01427598670125008</v>
+        <v>-0.01517869904637337</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.005550052970647812</v>
+        <v>-0.005523025989532471</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.003366231918334961</v>
+        <v>-0.007062714546918869</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.006208177655935287</v>
+        <v>0.005419522523880005</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.006376218050718307</v>
+        <v>-0.009095277637243271</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.00506109744310379</v>
+        <v>-0.007636219263076782</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.005635648965835571</v>
+        <v>0.003327589482069016</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.009151063859462738</v>
+        <v>0.004741083830595016</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.01376615092158318</v>
+        <v>0.01334771886467934</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.01669330894947052</v>
+        <v>0.01522050425410271</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.002577651292085648</v>
+        <v>-0.002567440271377563</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.02316978201270103</v>
+        <v>0.01798978075385094</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.2599999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.007328670471906662</v>
+        <v>-0.008404240012168884</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.1199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.02442637830972672</v>
+        <v>0.02120664343237877</v>
       </c>
       <c r="JB82" t="n">
         <v>0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.01576020196080208</v>
+        <v>0.01526065543293953</v>
       </c>
       <c r="JB83" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.01732603460550308</v>
+        <v>0.01764363050460815</v>
       </c>
       <c r="JB84" t="n">
         <v>0.3</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.02423679456114769</v>
+        <v>-0.02254420146346092</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0.2783707547424303</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.02129619941115379</v>
+        <v>0.02084687352180481</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
         <v>0.2783722246821034</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.02239086478948593</v>
+        <v>0.02200323715806007</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0.2783734741308254</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.004268940538167953</v>
+        <v>0.003160953521728516</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0.2783748338250227</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.0498722605407238</v>
+        <v>0.04904788732528687</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0.2783726289155134</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.01099774613976479</v>
+        <v>0.009354669600725174</v>
       </c>
       <c r="JB90" t="n">
         <v>0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.03551267087459564</v>
+        <v>0.03196670487523079</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.02101528644561768</v>
+        <v>0.02015745639801025</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.16</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0.2783719306941687</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.002261895686388016</v>
+        <v>0.001168664544820786</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0054205022752285</v>
+        <v>-0.005741633474826813</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.01214448735117912</v>
+        <v>-0.01277022436261177</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0.2783713794667914</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.005838979035615921</v>
+        <v>0.003018986433744431</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0.2783709384848895</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.003923472017049789</v>
+        <v>0.001156758517026901</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0.2783708282394139</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.0004674419760704041</v>
+        <v>-0.003688644617795944</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0.2783707914909222</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.004841025918722153</v>
+        <v>-0.005540844053030014</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0.2783709384848895</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0158076323568821</v>
+        <v>0.01365513727068901</v>
       </c>
       <c r="JB100" t="n">
         <v>0.02000000000000007</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.001312863081693649</v>
+        <v>-0.002253066748380661</v>
       </c>
       <c r="JB101" t="n">
         <v>0.02000000000000007</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.005732234567403793</v>
+        <v>0.004762742668390274</v>
       </c>
       <c r="JB102" t="n">
         <v>0.02000000000000007</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.00528142973780632</v>
+        <v>-0.005852803587913513</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0.278371048730365</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.004568841308355331</v>
+        <v>-0.007916141301393509</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.008046429604291916</v>
+        <v>-0.008605930954217911</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.01021180674433708</v>
+        <v>-0.009839139878749847</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.01806877925992012</v>
+        <v>-0.01893579587340355</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.01431823894381523</v>
+        <v>-0.01525625959038734</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002426590770483017</v>
+        <v>-0.001957077533006668</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.01382211223244667</v>
+        <v>-0.01474476233124733</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.00118589773774147</v>
+        <v>-4.30569052696228e-05</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
         <v>0.2783694685452166</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.002997376024723053</v>
+        <v>-0.003924071788787842</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
         <v>0.2783695420422002</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.006336085498332977</v>
+        <v>0.006825219839811325</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="JC113" t="n">
         <v>0.2783695787906921</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.02107853814959526</v>
+        <v>-0.02205782011151314</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.009466860443353653</v>
+        <v>0.00710596889257431</v>
       </c>
       <c r="JB115" t="n">
         <v>0.5799999999999998</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.008116502314805984</v>
+        <v>0.003543686121702194</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0.278369799281643</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01227801293134689</v>
+        <v>0.0118313767015934</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0.2783697625331511</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.01355800777673721</v>
+        <v>0.01263725385069847</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0.2783696890361674</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01575061678886414</v>
+        <v>0.01520330086350441</v>
       </c>
       <c r="JB119" t="n">
         <v>0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.01169585064053535</v>
+        <v>0.01123885437846184</v>
       </c>
       <c r="JB120" t="n">
         <v>0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.01604077965021133</v>
+        <v>0.01337717846035957</v>
       </c>
       <c r="JB121" t="n">
         <v>0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0147521011531353</v>
+        <v>0.01426847279071808</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.01689591258764267</v>
+        <v>0.01636176556348801</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.005618546158075333</v>
+        <v>0.003832820802927017</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.01448942348361015</v>
+        <v>-0.01486321166157722</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.1600000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.03651267662644386</v>
+        <v>0.03565062582492828</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3000000000000004</v>
